--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -922,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119510441</v>
+        <v>119510505</v>
       </c>
       <c r="B4" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,16 +938,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -958,7 +958,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521828</v>
+        <v>521846</v>
       </c>
       <c r="R4" t="n">
-        <v>6718916</v>
+        <v>6718897</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1017,12 +1017,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På tall, intill annan ringhackad med färska spår.</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,10 +1044,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119510505</v>
+        <v>119510441</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,16 +1060,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1085,7 +1080,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1099,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521846</v>
+        <v>521828</v>
       </c>
       <c r="R5" t="n">
-        <v>6718897</v>
+        <v>6718916</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1134,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1144,7 +1139,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tall, intill annan ringhackad med färska spår.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1297,10 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119528057</v>
+        <v>119529497</v>
       </c>
       <c r="B7" t="n">
-        <v>90334</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1309,35 +1309,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1346,13 +1347,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521691</v>
+        <v>521835</v>
       </c>
       <c r="R7" t="n">
-        <v>6718816</v>
+        <v>6718809</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1381,7 +1382,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1391,7 +1392,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1406,22 +1407,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119193397</v>
+        <v>119528057</v>
       </c>
       <c r="B8" t="n">
-        <v>57310</v>
+        <v>90334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1430,36 +1431,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521699</v>
+        <v>521691</v>
       </c>
       <c r="R8" t="n">
-        <v>6718868</v>
+        <v>6718816</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1498,27 +1498,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På grövre gran</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1533,22 +1528,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119529497</v>
+        <v>119193397</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1561,16 +1556,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1581,7 +1576,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1595,10 +1590,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521835</v>
+        <v>521699</v>
       </c>
       <c r="R9" t="n">
-        <v>6718809</v>
+        <v>6718868</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1625,22 +1620,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På grövre gran</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -1900,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119658245</v>
+        <v>119658241</v>
       </c>
       <c r="B12" t="n">
         <v>91494</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521685</v>
+        <v>521689</v>
       </c>
       <c r="R12" t="n">
-        <v>6718841</v>
+        <v>6718804</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119658241</v>
+        <v>119652338</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
+        <v>4766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2040,48 +2040,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521689</v>
+        <v>521702</v>
       </c>
       <c r="R13" t="n">
-        <v>6718804</v>
+        <v>6718828</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2110,7 +2104,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2120,7 +2114,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2129,7 +2123,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2148,10 +2141,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119652338</v>
+        <v>119658245</v>
       </c>
       <c r="B14" t="n">
-        <v>4766</v>
+        <v>91494</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,42 +2157,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521702</v>
+        <v>521685</v>
       </c>
       <c r="R14" t="n">
-        <v>6718828</v>
+        <v>6718841</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2228,7 +2227,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2238,7 +2237,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,6 +2246,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2755,7 +2755,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119810610</v>
+        <v>119825826</v>
       </c>
       <c r="B19" t="n">
         <v>5189</v>
@@ -2789,24 +2789,28 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521814</v>
+        <v>521644</v>
       </c>
       <c r="R19" t="n">
-        <v>6718954</v>
+        <v>6718845</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2830,22 +2834,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,6 +2858,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2872,10 +2877,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119810532</v>
+        <v>119810610</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2888,21 +2893,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2989,10 +2994,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119825826</v>
+        <v>119810532</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3005,46 +3010,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521644</v>
+        <v>521814</v>
       </c>
       <c r="R21" t="n">
-        <v>6718845</v>
+        <v>6718954</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3068,22 +3069,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3092,7 +3093,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -1900,7 +1900,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119658241</v>
+        <v>119658245</v>
       </c>
       <c r="B12" t="n">
         <v>91494</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521689</v>
+        <v>521685</v>
       </c>
       <c r="R12" t="n">
-        <v>6718804</v>
+        <v>6718841</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119652338</v>
+        <v>119658241</v>
       </c>
       <c r="B13" t="n">
-        <v>4766</v>
+        <v>91494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2040,42 +2040,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>521702</v>
+        <v>521689</v>
       </c>
       <c r="R13" t="n">
-        <v>6718828</v>
+        <v>6718804</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2104,7 +2110,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2114,7 +2120,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,6 +2129,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2141,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119658245</v>
+        <v>119652338</v>
       </c>
       <c r="B14" t="n">
-        <v>91494</v>
+        <v>4766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2157,48 +2164,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521685</v>
+        <v>521702</v>
       </c>
       <c r="R14" t="n">
-        <v>6718841</v>
+        <v>6718828</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2227,7 +2228,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2237,7 +2238,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2246,7 +2247,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2508,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786126</v>
+        <v>119786320</v>
       </c>
       <c r="B17" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2520,40 +2520,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2562,13 +2557,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521861</v>
+        <v>521830</v>
       </c>
       <c r="R17" t="n">
-        <v>6718940</v>
+        <v>6718954</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2597,7 +2592,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2607,7 +2602,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2634,10 +2629,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119786320</v>
+        <v>119786126</v>
       </c>
       <c r="B18" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2646,35 +2641,40 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521830</v>
+        <v>521861</v>
       </c>
       <c r="R18" t="n">
-        <v>6718954</v>
+        <v>6718940</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119825826</v>
+        <v>119810610</v>
       </c>
       <c r="B19" t="n">
         <v>5189</v>
@@ -2789,28 +2789,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521644</v>
+        <v>521814</v>
       </c>
       <c r="R19" t="n">
-        <v>6718845</v>
+        <v>6718954</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2834,22 +2830,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2858,7 +2854,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2877,10 +2872,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119810610</v>
+        <v>119825819</v>
       </c>
       <c r="B20" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2893,42 +2888,46 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521814</v>
+        <v>521644</v>
       </c>
       <c r="R20" t="n">
-        <v>6718954</v>
+        <v>6718845</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2952,22 +2951,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2976,6 +2975,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3111,10 +3111,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119825819</v>
+        <v>119825826</v>
       </c>
       <c r="B22" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,21 +3127,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -2508,10 +2508,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786320</v>
+        <v>119786126</v>
       </c>
       <c r="B17" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2520,35 +2520,40 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2557,13 +2562,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521830</v>
+        <v>521861</v>
       </c>
       <c r="R17" t="n">
-        <v>6718954</v>
+        <v>6718940</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2592,7 +2597,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2602,7 +2607,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2629,10 +2634,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119786126</v>
+        <v>119786320</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2641,40 +2646,35 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2683,13 +2683,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521861</v>
+        <v>521830</v>
       </c>
       <c r="R18" t="n">
-        <v>6718940</v>
+        <v>6718954</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,10 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119810610</v>
+        <v>119810532</v>
       </c>
       <c r="B19" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119825819</v>
+        <v>119810610</v>
       </c>
       <c r="B20" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2888,46 +2888,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521644</v>
+        <v>521814</v>
       </c>
       <c r="R20" t="n">
-        <v>6718845</v>
+        <v>6718954</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2951,22 +2947,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2975,7 +2971,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2994,10 +2989,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119810532</v>
+        <v>119825819</v>
       </c>
       <c r="B21" t="n">
-        <v>5169</v>
+        <v>4766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3010,42 +3005,46 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521814</v>
+        <v>521644</v>
       </c>
       <c r="R21" t="n">
-        <v>6718954</v>
+        <v>6718845</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3069,22 +3068,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3093,6 +3092,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3236,7 +3236,7 @@
         <v>119874841</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3503,7 +3503,7 @@
         <v>119923684</v>
       </c>
       <c r="B25" t="n">
-        <v>56514</v>
+        <v>56524</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -2755,10 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119810532</v>
+        <v>119825826</v>
       </c>
       <c r="B19" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,42 +2771,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521814</v>
+        <v>521644</v>
       </c>
       <c r="R19" t="n">
-        <v>6718954</v>
+        <v>6718845</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2830,22 +2834,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2854,6 +2858,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3111,10 +3116,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119825826</v>
+        <v>119810532</v>
       </c>
       <c r="B22" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3127,46 +3132,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521644</v>
+        <v>521814</v>
       </c>
       <c r="R22" t="n">
-        <v>6718845</v>
+        <v>6718954</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3190,22 +3191,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3214,7 +3215,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -2755,10 +2755,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119825826</v>
+        <v>119825819</v>
       </c>
       <c r="B19" t="n">
-        <v>5189</v>
+        <v>4766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,21 +2771,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>105930</v>
+        <v>100299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2877,10 +2877,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119810610</v>
+        <v>119810532</v>
       </c>
       <c r="B20" t="n">
-        <v>5189</v>
+        <v>5169</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2893,21 +2893,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2994,10 +2994,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119825819</v>
+        <v>119825826</v>
       </c>
       <c r="B21" t="n">
-        <v>4766</v>
+        <v>5189</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3010,21 +3010,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3116,10 +3116,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119810532</v>
+        <v>119810610</v>
       </c>
       <c r="B22" t="n">
-        <v>5169</v>
+        <v>5189</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3132,21 +3132,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3617,7 +3617,7 @@
         <v>120973036</v>
       </c>
       <c r="B26" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>121177422</v>
       </c>
       <c r="B27" t="n">
-        <v>90687</v>
+        <v>90697</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3617,7 +3617,7 @@
         <v>120973036</v>
       </c>
       <c r="B26" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3753,7 +3753,7 @@
         <v>121177422</v>
       </c>
       <c r="B27" t="n">
-        <v>90697</v>
+        <v>90709</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3753,7 +3753,7 @@
         <v>121177422</v>
       </c>
       <c r="B27" t="n">
-        <v>90709</v>
+        <v>90710</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3753,7 +3753,7 @@
         <v>121177422</v>
       </c>
       <c r="B27" t="n">
-        <v>90710</v>
+        <v>90713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3753,7 +3753,7 @@
         <v>121177422</v>
       </c>
       <c r="B27" t="n">
-        <v>90713</v>
+        <v>90719</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119186194</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         <v>119479577</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>119510441</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>119193397</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3869,6 +3869,385 @@
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>124837870</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>521694</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6718895</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera äldre fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>124838208</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>521735</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6718890</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>124838112</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>521734</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6718890</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124837870</v>
+        <v>124838208</v>
       </c>
       <c r="B28" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,38 +3883,57 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521694</v>
+        <v>521735</v>
       </c>
       <c r="R28" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3946,7 +3965,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3956,12 +3975,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3988,7 +4007,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838208</v>
+        <v>124838112</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -4023,7 +4042,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4036,18 +4055,13 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521735</v>
+        <v>521734</v>
       </c>
       <c r="R29" t="n">
         <v>6718890</v>
@@ -4082,7 +4096,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4092,12 +4106,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,10 +4133,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838112</v>
+        <v>124837870</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,52 +4145,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521734</v>
+        <v>521694</v>
       </c>
       <c r="R30" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4213,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4223,7 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838208</v>
+        <v>124837870</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,57 +3883,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521735</v>
+        <v>521694</v>
       </c>
       <c r="R28" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3965,7 +3946,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3975,12 +3956,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4133,10 +4114,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837870</v>
+        <v>124838208</v>
       </c>
       <c r="B30" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4145,38 +4126,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521694</v>
+        <v>521735</v>
       </c>
       <c r="R30" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3988,7 +3988,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838112</v>
+        <v>124838208</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4036,13 +4036,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521734</v>
+        <v>521735</v>
       </c>
       <c r="R29" t="n">
         <v>6718890</v>
@@ -4077,7 +4082,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4087,7 +4092,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4114,7 +4124,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838208</v>
+        <v>124838112</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -4149,7 +4159,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4162,18 +4172,13 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521735</v>
+        <v>521734</v>
       </c>
       <c r="R30" t="n">
         <v>6718890</v>
@@ -4208,7 +4213,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4223,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124837870</v>
+        <v>124838112</v>
       </c>
       <c r="B28" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,38 +3883,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521694</v>
+        <v>521734</v>
       </c>
       <c r="R28" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3946,7 +3960,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3956,12 +3970,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4124,10 +4133,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838112</v>
+        <v>124837870</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,52 +4145,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521734</v>
+        <v>521694</v>
       </c>
       <c r="R30" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4213,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4223,7 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,7 +3871,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838112</v>
+        <v>124838208</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3919,13 +3919,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521734</v>
+        <v>521735</v>
       </c>
       <c r="R28" t="n">
         <v>6718890</v>
@@ -3960,7 +3965,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3970,7 +3975,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3997,10 +4007,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838208</v>
+        <v>124837870</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4009,57 +4019,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521735</v>
+        <v>521694</v>
       </c>
       <c r="R29" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4091,7 +4082,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4101,12 +4092,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4133,10 +4124,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837870</v>
+        <v>124838112</v>
       </c>
       <c r="B30" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4145,38 +4136,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521694</v>
+        <v>521734</v>
       </c>
       <c r="R30" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,7 +4213,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4223,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,7 +3871,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838208</v>
+        <v>124838112</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3919,18 +3919,13 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521735</v>
+        <v>521734</v>
       </c>
       <c r="R28" t="n">
         <v>6718890</v>
@@ -3965,7 +3960,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3975,12 +3970,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4007,10 +3997,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124837870</v>
+        <v>124838208</v>
       </c>
       <c r="B29" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4019,38 +4009,57 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521694</v>
+        <v>521735</v>
       </c>
       <c r="R29" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4082,7 +4091,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4092,12 +4101,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,10 +4133,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838112</v>
+        <v>124837870</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4136,52 +4145,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521734</v>
+        <v>521694</v>
       </c>
       <c r="R30" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4213,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4223,7 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838112</v>
+        <v>124837870</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,52 +3883,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521734</v>
+        <v>521694</v>
       </c>
       <c r="R28" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3960,7 +3946,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3970,7 +3956,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4133,10 +4124,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837870</v>
+        <v>124838112</v>
       </c>
       <c r="B30" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4145,38 +4136,52 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521694</v>
+        <v>521734</v>
       </c>
       <c r="R30" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,7 +4213,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4223,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124837870</v>
+        <v>124838112</v>
       </c>
       <c r="B28" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,38 +3883,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521694</v>
+        <v>521734</v>
       </c>
       <c r="R28" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3946,7 +3960,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3956,12 +3970,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3988,10 +3997,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838208</v>
+        <v>124837870</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4000,57 +4009,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521735</v>
+        <v>521694</v>
       </c>
       <c r="R29" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4082,7 +4072,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4092,12 +4082,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4124,7 +4114,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838112</v>
+        <v>124838208</v>
       </c>
       <c r="B30" t="n">
         <v>98101</v>
@@ -4159,7 +4149,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4172,13 +4162,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521734</v>
+        <v>521735</v>
       </c>
       <c r="R30" t="n">
         <v>6718890</v>
@@ -4213,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4223,7 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,7 +3871,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838112</v>
+        <v>124838208</v>
       </c>
       <c r="B28" t="n">
         <v>98101</v>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3919,13 +3919,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521734</v>
+        <v>521735</v>
       </c>
       <c r="R28" t="n">
         <v>6718890</v>
@@ -3960,7 +3965,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3970,7 +3975,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3997,10 +4007,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124837870</v>
+        <v>124838112</v>
       </c>
       <c r="B29" t="n">
-        <v>91032</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4009,38 +4019,52 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521694</v>
+        <v>521734</v>
       </c>
       <c r="R29" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4072,7 +4096,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4082,12 +4106,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4114,10 +4133,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838208</v>
+        <v>124837870</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4126,57 +4145,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521735</v>
+        <v>521694</v>
       </c>
       <c r="R30" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838208</v>
+        <v>124837870</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>91186</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3883,57 +3883,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521735</v>
+        <v>521694</v>
       </c>
       <c r="R28" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3965,7 +3946,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3975,12 +3956,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4010,7 +3991,7 @@
         <v>124838112</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4133,10 +4114,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837870</v>
+        <v>124838208</v>
       </c>
       <c r="B30" t="n">
-        <v>91032</v>
+        <v>98269</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4145,38 +4126,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521694</v>
+        <v>521735</v>
       </c>
       <c r="R30" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3988,7 +3988,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838112</v>
+        <v>124838208</v>
       </c>
       <c r="B29" t="n">
         <v>98269</v>
@@ -4023,7 +4023,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -4036,13 +4036,18 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521734</v>
+        <v>521735</v>
       </c>
       <c r="R29" t="n">
         <v>6718890</v>
@@ -4077,7 +4082,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4087,7 +4092,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4114,7 +4124,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838208</v>
+        <v>124838112</v>
       </c>
       <c r="B30" t="n">
         <v>98269</v>
@@ -4149,7 +4159,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4162,18 +4172,13 @@
           <t>fullt utvecklade blad</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521735</v>
+        <v>521734</v>
       </c>
       <c r="R30" t="n">
         <v>6718890</v>
@@ -4208,7 +4213,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4218,12 +4223,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:53</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -3871,50 +3871,59 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124837870</v>
+        <v>124838112</v>
       </c>
       <c r="B28" t="n">
-        <v>91186</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98269</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521694</v>
+        <v>521734</v>
       </c>
       <c r="R28" t="n">
-        <v>6718895</v>
+        <v>6718890</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3946,7 +3955,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3956,12 +3965,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3993,11 +3997,6 @@
       <c r="B29" t="n">
         <v>98269</v>
       </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>VU</t>
@@ -4124,64 +4123,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124838112</v>
+        <v>124837870</v>
       </c>
       <c r="B30" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91186</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521734</v>
+        <v>521694</v>
       </c>
       <c r="R30" t="n">
-        <v>6718890</v>
+        <v>6718895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4213,7 +4193,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4223,7 +4203,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Flera äldre fruktkroppar.</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119186194</v>
+        <v>119785591</v>
       </c>
       <c r="B2" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521695</v>
+        <v>521845</v>
       </c>
       <c r="R2" t="n">
-        <v>6718812</v>
+        <v>6718745</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-17</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hyfsat färska spår. Gran, ringhack runt hela stammen.</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,27 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119479577</v>
+        <v>121177422</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,27 +793,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>521846</v>
+        <v>521806</v>
       </c>
       <c r="R3" t="n">
-        <v>6718922</v>
+        <v>6718961</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,27 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-01</t>
+          <t>2024-11-14</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På tall, savar från hål, barken ser färskfläkt ut.</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,27 +886,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Maria Warg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119510505</v>
+        <v>119849702</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,47 +909,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521846</v>
+        <v>521703</v>
       </c>
       <c r="R4" t="n">
-        <v>6718897</v>
+        <v>6718807</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,22 +963,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:05</t>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikt på två granlågor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,60 +998,54 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119510441</v>
+        <v>119528057</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1094,13 +1054,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521828</v>
+        <v>521691</v>
       </c>
       <c r="R5" t="n">
-        <v>6718916</v>
+        <v>6718816</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,27 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:01</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På tall, intill annan ringhackad med färska spår.</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,27 +1114,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119510778</v>
+        <v>119527938</v>
       </c>
       <c r="B6" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,36 +1137,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1225,13 +1170,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521839</v>
+        <v>521725</v>
       </c>
       <c r="R6" t="n">
-        <v>6718798</v>
+        <v>6718832</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,22 +1200,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-02</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,27 +1230,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119529497</v>
+        <v>119786320</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,32 +1253,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1347,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>521835</v>
+        <v>521830</v>
       </c>
       <c r="R7" t="n">
-        <v>6718809</v>
+        <v>6718954</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1377,22 +1316,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1407,54 +1346,49 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119528057</v>
+        <v>119810705</v>
       </c>
       <c r="B8" t="n">
-        <v>90334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1468,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>521691</v>
+        <v>521827</v>
       </c>
       <c r="R8" t="n">
-        <v>6718816</v>
+        <v>6718967</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1498,22 +1432,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,15 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119193397</v>
+        <v>119825778</v>
       </c>
       <c r="B9" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,47 +1485,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>521699</v>
+        <v>521725</v>
       </c>
       <c r="R9" t="n">
-        <v>6718868</v>
+        <v>6718819</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1620,27 +1550,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-18</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På grövre gran</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1649,71 +1574,76 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119527192</v>
+        <v>119598207</v>
       </c>
       <c r="B10" t="n">
-        <v>97941</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>4368</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>521818</v>
+        <v>521663</v>
       </c>
       <c r="R10" t="n">
-        <v>6718850</v>
+        <v>6718832</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1737,22 +1667,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-09-03</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1767,27 +1697,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119598207</v>
+        <v>119650637</v>
       </c>
       <c r="B11" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93215</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1739,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1828,13 +1753,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>521663</v>
+        <v>521666</v>
       </c>
       <c r="R11" t="n">
-        <v>6718832</v>
+        <v>6718818</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,22 +1783,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,54 +1813,49 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119658245</v>
+        <v>119528335</v>
       </c>
       <c r="B12" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4769</v>
+        <v>4404</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1943,21 +1863,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>521685</v>
+        <v>521703</v>
       </c>
       <c r="R12" t="n">
-        <v>6718841</v>
+        <v>6718880</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1981,22 +1899,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,7 +1923,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2027,12 +1944,7 @@
         <v>119658241</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2054,7 +1966,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2148,15 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119652338</v>
+        <v>119658245</v>
       </c>
       <c r="B14" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,42 +2071,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100299</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>521702</v>
+        <v>521685</v>
       </c>
       <c r="R14" t="n">
-        <v>6718828</v>
+        <v>6718841</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2228,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2238,7 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2247,6 +2160,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2265,58 +2179,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119665792</v>
+        <v>119789430</v>
       </c>
       <c r="B15" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100299</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>521685</v>
+        <v>521734</v>
       </c>
       <c r="R15" t="n">
-        <v>6718841</v>
+        <v>6718966</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,27 +2253,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:19</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>50cm bh</t>
+          <t>13:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2387,47 +2295,43 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119650637</v>
+        <v>119510505</v>
       </c>
       <c r="B16" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4368</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2436,13 +2340,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>521666</v>
+        <v>521846</v>
       </c>
       <c r="R16" t="n">
-        <v>6718818</v>
+        <v>6718897</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2466,22 +2370,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>19:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,44 +2400,39 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119786126</v>
+        <v>119510778</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2546,29 +2445,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>födosökande</t>
         </is>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>521861</v>
+        <v>521839</v>
       </c>
       <c r="R17" t="n">
-        <v>6718940</v>
+        <v>6718798</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2592,22 +2491,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2622,27 +2521,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119786320</v>
+        <v>119529497</v>
       </c>
       <c r="B18" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2650,31 +2544,32 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2683,13 +2578,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>521830</v>
+        <v>521835</v>
       </c>
       <c r="R18" t="n">
-        <v>6718954</v>
+        <v>6718809</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2713,22 +2608,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-03</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2743,27 +2638,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119825819</v>
+        <v>119785227</v>
       </c>
       <c r="B19" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2771,46 +2661,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>521644</v>
+        <v>521718</v>
       </c>
       <c r="R19" t="n">
-        <v>6718845</v>
+        <v>6718801</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2839,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2849,7 +2739,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Minst en kan vara två</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2858,7 +2753,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2877,58 +2771,56 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119810532</v>
+        <v>119186194</v>
       </c>
       <c r="B20" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>521814</v>
+        <v>521695</v>
       </c>
       <c r="R20" t="n">
-        <v>6718954</v>
+        <v>6718812</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2952,22 +2844,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-08-17</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>19:01</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Hyfsat färska spår. Gran, ringhack runt hela stammen.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2982,44 +2879,39 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119825826</v>
+        <v>119193397</v>
       </c>
       <c r="B21" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3028,28 +2920,29 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521644</v>
+        <v>521699</v>
       </c>
       <c r="R21" t="n">
-        <v>6718845</v>
+        <v>6718868</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3073,22 +2966,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-08-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På grövre gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3097,51 +2995,45 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119810610</v>
+        <v>119479577</v>
       </c>
       <c r="B22" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>105930</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3152,7 +3044,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3161,13 +3053,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521814</v>
+        <v>521846</v>
       </c>
       <c r="R22" t="n">
-        <v>6718954</v>
+        <v>6718922</v>
       </c>
       <c r="S22" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3191,22 +3083,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-09-17</t>
+          <t>2024-09-01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På tall, savar från hål, barken ser färskfläkt ut.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3221,27 +3118,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119874841</v>
+        <v>119510441</v>
       </c>
       <c r="B23" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,19 +3158,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3292,13 +3175,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521846</v>
+        <v>521828</v>
       </c>
       <c r="R23" t="n">
-        <v>6718801</v>
+        <v>6718916</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3322,27 +3205,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-09-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På skadad gran.</t>
+          <t>På tall, intill annan ringhackad med färska spår.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3369,15 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119922094</v>
+        <v>121222588</v>
       </c>
       <c r="B24" t="n">
-        <v>5266</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3385,43 +3263,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100155</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre timmerman</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Acanthocinus griseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fabricius, 1792)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>521859</v>
+        <v>521868</v>
       </c>
       <c r="R24" t="n">
-        <v>6718776</v>
+        <v>6718944</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3448,17 +3327,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Larver i diffusa gångsystem under bark i ögonhöjd, en larv tas tillvara, och granskas mot bestämningslitteratur</t>
+          <t>Två tallar med ringhack.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3469,46 +3358,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Barrblandskog, naturskogsartad</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Gran dödad av granbarkborre året innan</t>
-        </is>
-      </c>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>Lars-Ove Wikars</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119923684</v>
+        <v>121222701</v>
       </c>
       <c r="B25" t="n">
-        <v>56524</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3516,16 +3385,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3533,32 +3402,30 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stormyran, Dlr</t>
+          <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521887</v>
+        <v>521874</v>
       </c>
       <c r="R25" t="n">
-        <v>6718834</v>
+        <v>6718912</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3582,12 +3449,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-09-20</t>
+          <t>2024-11-17</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack på gran, färska spår intill yttre gräns där stora enso ska avverka.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3602,69 +3484,50 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Bo karlstens</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lars-Ove Wikars</t>
+          <t>Karl Ericson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120973036</v>
+        <v>119648958</v>
       </c>
       <c r="B26" t="n">
-        <v>98094</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3673,13 +3536,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>521721</v>
+        <v>521817</v>
       </c>
       <c r="R26" t="n">
-        <v>6718896</v>
+        <v>6718754</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3703,27 +3566,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter inom ca 1kvm.</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3738,59 +3596,50 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121177422</v>
+        <v>119651942</v>
       </c>
       <c r="B27" t="n">
-        <v>90719</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>100299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3799,13 +3648,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>521806</v>
+        <v>521719</v>
       </c>
       <c r="R27" t="n">
-        <v>6718961</v>
+        <v>6718887</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3829,22 +3678,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-14</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3859,59 +3708,50 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Maria Warg</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124838112</v>
+        <v>119652338</v>
       </c>
       <c r="B28" t="n">
-        <v>98269</v>
+        <v>4775</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3920,13 +3760,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>521734</v>
+        <v>521702</v>
       </c>
       <c r="R28" t="n">
-        <v>6718890</v>
+        <v>6718828</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3950,22 +3790,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-09</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3980,76 +3820,62 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124838208</v>
+        <v>119665792</v>
       </c>
       <c r="B29" t="n">
-        <v>98269</v>
+        <v>4775</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stormyran, Stormyran, Dlr</t>
+          <t>Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>521735</v>
+        <v>521685</v>
       </c>
       <c r="R29" t="n">
-        <v>6718890</v>
+        <v>6718841</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4076,27 +3902,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Intill grövre tall och senvuxen klen gran.</t>
+          <t>50cm bh</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4111,60 +3937,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Karl Ericson</t>
+          <t>Bo karlstens</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124837870</v>
+        <v>119813225</v>
       </c>
       <c r="B30" t="n">
-        <v>91186</v>
+        <v>4775</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>100299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Stormyran, Stormyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>521694</v>
+        <v>521872</v>
       </c>
       <c r="R30" t="n">
-        <v>6718895</v>
+        <v>6718910</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4188,27 +4019,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-17</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flera äldre fruktkroppar.</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4223,15 +4049,1753 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>119825819</v>
+      </c>
+      <c r="B31" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>521644</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6718845</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>119651875</v>
+      </c>
+      <c r="B32" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>521719</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6718887</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>119785616</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>521845</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6718745</v>
+      </c>
+      <c r="S33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>119810532</v>
+      </c>
+      <c r="B34" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>521814</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6718954</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>119821503</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>521786</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6718861</v>
+      </c>
+      <c r="S35" t="n">
+        <v>9</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>119923684</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>521887</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6718834</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-09-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>119651925</v>
+      </c>
+      <c r="B37" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>521719</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6718887</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>119810610</v>
+      </c>
+      <c r="B38" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>521814</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6718954</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>119821527</v>
+      </c>
+      <c r="B39" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>521786</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6718861</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-09-17</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Även Thomsons tg</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>119825826</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>521644</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6718845</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>119527192</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>521818</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6718850</v>
+      </c>
+      <c r="S41" t="n">
+        <v>9</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>119528414</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>521730</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6718879</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-09-03</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bo karlstens</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120973036</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>521721</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6718896</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-11-06</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter inom ca 1kvm.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>Karl Ericson</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>124838112</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>521734</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6718890</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>124838208</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Stormyran, Stormyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>521735</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6718890</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Aspeboda</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:53</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Intill grövre tall och senvuxen klen gran.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32722-2024 artfynd.xlsx
+++ b/artfynd/A 32722-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AZ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785591</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -895,6 +905,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121177422</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119849702</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528057</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119527938</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,6 +1385,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119786320</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1471,6 +1506,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810705</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1590,6 +1630,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119825778</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1706,6 +1751,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119598207</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1822,6 +1872,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119650637</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1938,6 +1993,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528335</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,6 +2117,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119658241</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2176,6 +2241,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119658245</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2292,6 +2362,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119789430</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2409,6 +2484,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119510505</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2530,6 +2610,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119510778</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2647,6 +2732,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119529497</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2768,6 +2858,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785227</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2888,6 +2983,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119186194</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3010,6 +3110,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119193397</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3127,6 +3232,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119479577</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3249,6 +3359,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119510441</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3371,6 +3486,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121222588</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3493,6 +3613,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121222701</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3605,6 +3730,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119648958</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3717,6 +3847,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651942</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3829,6 +3964,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119652338</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3946,6 +4086,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119665792</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4058,6 +4203,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119813225</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4175,6 +4325,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119825819</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4287,6 +4442,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651875</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4399,6 +4559,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119785616</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4511,6 +4676,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810532</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4623,6 +4793,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119821503</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4732,6 +4907,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119923684</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4844,6 +5024,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119651925</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4956,6 +5141,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119810610</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5073,6 +5263,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119821527</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5190,6 +5385,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119825826</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5297,6 +5497,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119527192</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5413,6 +5618,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119528414</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5544,6 +5754,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120973036</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5665,6 +5880,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838112</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5796,8 +6016,59 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124838208</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>